--- a/control_acceso/reportellegadasAdministrativos.xlsx
+++ b/control_acceso/reportellegadasAdministrativos.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +27,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
     </font>
   </fonts>
   <fills count="2">
@@ -59,14 +55,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -435,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -446,82 +436,176 @@
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="n"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>documento</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>llegadas_tarde</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>llegadas_a_tiempo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sin_marcar</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>total_registros</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cumplimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Arrieta Lopez Benito Antonio</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>78108535</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>63.64</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bermudez Arango Diana Patricia</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>43738701</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Berrio Gomez Astrid Vanessa</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1000400420</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>81.81999999999999</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>nombre</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>documento</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>llegadas_tarde</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>llegadas_a_tiempo</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>sin_marcar</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>total_registros</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>cumplimiento</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Botero Zabala Luz Miriyam</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>43208497</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>45.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arrieta Lopez Benito Antonio</t>
+          <t>Camero Arias Sidney Rosmary</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78108535</v>
+        <v>43798852</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>70</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bermudez Arango Diana Patricia</t>
+          <t>Cantor Tirado Maria Oliva</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43738701</v>
+        <v>43562594</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -530,10 +614,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -542,64 +626,64 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Berrio Gomez Astrid Vanessa</t>
+          <t>David Mercado Andres Felipe</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1000400420</v>
+        <v>1066183050</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Botero Zabala Luz Miriyam</t>
+          <t>Diaz Escudero Olga Lucia</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43208497</v>
+        <v>43584787</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Camero Arias Sidney Rosmary</t>
+          <t>Duque Claudia Ximena</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43798852</v>
+        <v>43273930</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -608,760 +692,660 @@
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cantor Tirado Maria Oliva</t>
+          <t>Estrada Perez Giovanny</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43562594</v>
+        <v>8356147</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>David Mercado Andres Felipe</t>
+          <t>Finke Teachout Marilyn Jean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1066183050</v>
+        <v>145250</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Diaz Escudero Olga Lucia</t>
+          <t>Gallo Quintero Alexandra</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43584787</v>
+        <v>1036650180</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Duque Claudia Ximena</t>
+          <t>Garcia Marin Liliana Maria</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>43273930</v>
+        <v>43539114</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Estrada Perez Giovanny</t>
+          <t>Gomez Giraldo Ruben Humberto</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8356147</v>
+        <v>71652891</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finke Teachout Marilyn Jean</t>
+          <t>Gonzalez Fuentes Edgar</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>145250</v>
+        <v>16678768</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gallo Quintero Alexandra</t>
+          <t>Gonzalez Viloria Ana Marelvis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1036650180</v>
+        <v>22797349</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Garcia Marin Liliana Maria</t>
+          <t>Hernandez Cuervo Karen Mayerlyn</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43539114</v>
+        <v>20829488</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gomez Giraldo Ruben Humberto</t>
+          <t>Hoyos Restrepo Lina Maria</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>71652891</v>
+        <v>43588915</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gonzalez Fuentes Edgar</t>
+          <t>Largo Guzman Juan Pablo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16678768</v>
+        <v>71334223</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gonzalez Viloria Ana Marelvis</t>
+          <t>Lujan Duran Lina Marcela</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22797349</v>
+        <v>43201717</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hernandez Cuervo Karen Mayerlyn</t>
+          <t>Montoya Goez Carlos Alfredo</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20829488</v>
+        <v>71333620</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hoyos Restrepo Lina Maria</t>
+          <t>Montoya Goez Wilton Fabio</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>43588915</v>
+        <v>71758931</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>70</v>
+        <v>90.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Largo Guzman Juan Pablo</t>
+          <t>Montoya Gomez Lina Maria</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>71334223</v>
+        <v>43838454</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lujan Duran Lina Marcela</t>
+          <t>Olarte Sanabria Lina Constanza</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>43201717</v>
+        <v>52030865</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Montoya Goez Carlos Alfredo</t>
+          <t>Ortiz Giraldo Diana Patricia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>71333620</v>
+        <v>43453085</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Montoya Goez Wilton Fabio</t>
+          <t>Osorno Lopera Richard Alonso</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>71758931</v>
+        <v>1037546222</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
         <v>7</v>
       </c>
-      <c r="E27" t="n">
-        <v>3</v>
-      </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Montoya Gomez Lina Maria</t>
+          <t>Patiño Gonzalez Karen Elien</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43838454</v>
+        <v>32182588</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>40</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Olarte Sanabria Lina Constanza</t>
+          <t>Perdomo Franco Laura Marcela</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52030865</v>
+        <v>1130642133</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ortiz Giraldo Diana Patricia</t>
+          <t>Rengifo Pardo Luz Yadira</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43453085</v>
+        <v>41946203</v>
       </c>
       <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
         <v>3</v>
       </c>
-      <c r="D30" t="n">
-        <v>6</v>
-      </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Osorno Lopera Richard Alonso</t>
+          <t>Rua Moreno Carmen Eliana</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1037546222</v>
+        <v>43590631</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>70</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Patiño Gonzalez Karen Elien</t>
+          <t>Sierra Ruiz Lina Maria</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32182588</v>
+        <v>43639788</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>30</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Perdomo Franco Laura Marcela</t>
+          <t>Solano Guevara Carlos Enrique</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1130642133</v>
+        <v>92502619</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rengifo Pardo Luz Yadira</t>
+          <t>Vidal Rojas Maria Cristina</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41946203</v>
+        <v>43168454</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>10</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rua Moreno Carmen Eliana</t>
+          <t>Yepes Arias Angela Maria</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>43590631</v>
+        <v>41945020</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>81.81999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sierra Ruiz Lina Maria</t>
+          <t>Álzate Montoya Sandra Elena</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>43639788</v>
+        <v>43743409</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Solano Guevara Carlos Enrique</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>92502619</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>9</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>10</v>
-      </c>
-      <c r="G37" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Vidal Rojas Maria Cristina</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>43168454</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>6</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
-      </c>
-      <c r="F38" t="n">
-        <v>10</v>
-      </c>
-      <c r="G38" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Yepes Arias Angela Maria</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>41945020</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Álzate Montoya Sandra Elena</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>43743409</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" t="n">
-        <v>10</v>
-      </c>
-      <c r="G40" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
     </row>
   </sheetData>

--- a/control_acceso/reportellegadasAdministrativos.xlsx
+++ b/control_acceso/reportellegadasAdministrativos.xlsx
@@ -483,19 +483,19 @@
         <v>78108535</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>63.64</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="3">
@@ -514,10 +514,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -533,19 +533,19 @@
         <v>1000400420</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>81.81999999999999</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="5">
@@ -558,19 +558,19 @@
         <v>43208497</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>45.45</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="6">
@@ -583,19 +583,19 @@
         <v>43798852</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>27.27</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="7">
@@ -611,16 +611,16 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>61.54</v>
       </c>
     </row>
     <row r="8">
@@ -633,19 +633,19 @@
         <v>1066183050</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>36.36</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="9">
@@ -658,19 +658,19 @@
         <v>43584787</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>54.55</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="10">
@@ -683,19 +683,19 @@
         <v>43273930</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>45.45</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="11">
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>81.81999999999999</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="12">
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -758,19 +758,19 @@
         <v>1036650180</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="14">
@@ -783,19 +783,19 @@
         <v>43539114</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>63.64</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="15">
@@ -808,19 +808,19 @@
         <v>71652891</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="16">
@@ -833,19 +833,19 @@
         <v>16678768</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>45.45</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="17">
@@ -858,19 +858,19 @@
         <v>22797349</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G17" t="n">
-        <v>54.55</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="18">
@@ -883,19 +883,19 @@
         <v>20829488</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>81.81999999999999</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="19">
@@ -911,16 +911,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>81.81999999999999</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="20">
@@ -933,19 +933,19 @@
         <v>71334223</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>45.45</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="21">
@@ -958,19 +958,19 @@
         <v>43201717</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="22">
@@ -986,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G22" t="n">
-        <v>81.81999999999999</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="23">
@@ -1011,16 +1011,16 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>90.91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -1033,19 +1033,19 @@
         <v>43838454</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
-        <v>63.64</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="25">
@@ -1058,19 +1058,19 @@
         <v>52030865</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>54.55</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="26">
@@ -1083,19 +1083,19 @@
         <v>43453085</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
-        <v>36.36</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="27">
@@ -1111,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G27" t="n">
-        <v>36.36</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="28">
@@ -1136,16 +1136,16 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>63.64</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="29">
@@ -1158,19 +1158,19 @@
         <v>1130642133</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>81.81999999999999</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="30">
@@ -1183,19 +1183,19 @@
         <v>41946203</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
-        <v>27.27</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="31">
@@ -1208,19 +1208,19 @@
         <v>43590631</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>54.55</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="32">
@@ -1233,19 +1233,19 @@
         <v>43639788</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G32" t="n">
-        <v>45.45</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="33">
@@ -1261,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>92.31</v>
       </c>
     </row>
     <row r="34">
@@ -1283,19 +1283,19 @@
         <v>43168454</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G34" t="n">
-        <v>63.64</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="35">
@@ -1308,7 +1308,7 @@
         <v>41945020</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>9</v>
@@ -1317,10 +1317,10 @@
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G35" t="n">
-        <v>81.81999999999999</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="36">
@@ -1333,19 +1333,19 @@
         <v>43743409</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
-        <v>45.45</v>
+        <v>84.62</v>
       </c>
     </row>
   </sheetData>
